--- a/templates/Cap_Huma_Modele_Import_Postes_VIERGE.xlsx
+++ b/templates/Cap_Huma_Modele_Import_Postes_VIERGE.xlsx
@@ -803,7 +803,7 @@
       <formula1>"Vacant,En recrutement"</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Expatrié,National"</formula1>
+      <formula1>"Expatrié,National,Détachement"</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Desk 1,Desk 2,Desk 3,SUO"</formula1>
